--- a/results/timeseries_PCA_UMAP_clustering.xlsx
+++ b/results/timeseries_PCA_UMAP_clustering.xlsx
@@ -1,18 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embeddings_Clusters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KMeans_Evaluation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KMeans_Clusters" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agglomerative_Clusters" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCA_Loadings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCA_Variance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Embeddings_Clusters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KMeans_Evaluation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PCA_Loadings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PCA_Variance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Analysis_Settings" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,52 +421,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>signal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>dataset</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>PC1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PC2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>UMAP1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>UMAP2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>KMeans_k2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Agglomerative_k3</t>
         </is>
@@ -488,12 +475,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sac_ascf_alpha</t>
+          <t>NLM_sac_ascf_alpha</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,20 +490,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sac_ascf_alpha.txt</t>
+          <t>NLM_sac_ascf_alpha.txt</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2881262349187524</v>
+        <v>1.869041941905772</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.947172269371595</v>
+        <v>-3.263338007383286</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2881262349187524</v>
+        <v>16.30864524841309</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.947172269371595</v>
+        <v>8.127042770385742</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -528,12 +515,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sac_ascf_beta</t>
+          <t>NLM_sac_ascf_beta</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -543,20 +530,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sac_ascf_beta.txt</t>
+          <t>NLM_sac_ascf_beta.txt</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.583914367586302</v>
+        <v>3.227774885136202</v>
       </c>
       <c r="F3" t="n">
-        <v>1.780180091201383</v>
+        <v>0.9467262620943137</v>
       </c>
       <c r="G3" t="n">
-        <v>2.583914367586302</v>
+        <v>13.76466655731201</v>
       </c>
       <c r="H3" t="n">
-        <v>1.780180091201383</v>
+        <v>7.335851669311523</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -568,12 +555,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sac_ascf_delta</t>
+          <t>NLM_sac_ascf_delta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -583,20 +570,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sac_ascf_delta.txt</t>
+          <t>NLM_sac_ascf_delta.txt</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-0.03597769890325492</v>
+        <v>1.175943211056967</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2976870559686169</v>
+        <v>-0.8466358079052689</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.03597769890325492</v>
+        <v>15.74817085266113</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2976870559686169</v>
+        <v>8.828913688659668</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -608,12 +595,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sac_ascf_gamma</t>
+          <t>NLM_sac_ascf_gamma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -623,37 +610,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sac_ascf_gamma.txt</t>
+          <t>NLM_sac_ascf_gamma.txt</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-4.052365640721468</v>
+        <v>-1.263199170790534</v>
       </c>
       <c r="F5" t="n">
-        <v>0.880184224507457</v>
+        <v>-0.8911135891304095</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.052365640721468</v>
+        <v>16.62538146972656</v>
       </c>
       <c r="H5" t="n">
-        <v>0.880184224507457</v>
+        <v>9.813300132751465</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sac_ascf_kai</t>
+          <t>NLM_sac_ascf_kai</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -663,20 +650,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sac_ascf_kai.txt</t>
+          <t>NLM_sac_ascf_kai.txt</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-12.14378091549097</v>
+        <v>-7.656855423136816</v>
       </c>
       <c r="F6" t="n">
-        <v>3.936940789131372</v>
+        <v>-0.9140165224585419</v>
       </c>
       <c r="G6" t="n">
-        <v>-12.14378091549097</v>
+        <v>18.00735282897949</v>
       </c>
       <c r="H6" t="n">
-        <v>3.936940789131372</v>
+        <v>9.92054271697998</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -688,12 +675,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sac_ascf_kappa</t>
+          <t>NLM_sac_ascf_kappa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -703,20 +690,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sac_ascf_kappa.txt</t>
+          <t>NLM_sac_ascf_kappa.txt</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.62285764351014</v>
+        <v>3.050222095212906</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9796488848645493</v>
+        <v>0.3210353268040089</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62285764351014</v>
+        <v>14.14610958099365</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9796488848645493</v>
+        <v>7.948673725128174</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -728,12 +715,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sac_ascf_lambda</t>
+          <t>NLM_sac_ascf_lambda</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -743,20 +730,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sac_ascf_lambda.txt</t>
+          <t>NLM_sac_ascf_lambda.txt</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.466307359841293</v>
+        <v>3.967435367716158</v>
       </c>
       <c r="F8" t="n">
-        <v>1.822737763774772</v>
+        <v>1.222785976452071</v>
       </c>
       <c r="G8" t="n">
-        <v>3.466307359841293</v>
+        <v>13.54347610473633</v>
       </c>
       <c r="H8" t="n">
-        <v>1.822737763774772</v>
+        <v>7.593661308288574</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -768,12 +755,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sac_ascf_mu</t>
+          <t>NLM_sac_ascf_mu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -783,20 +770,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sac_ascf_mu.txt</t>
+          <t>NLM_sac_ascf_mu.txt</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.429064618893106</v>
+        <v>4.165417000080113</v>
       </c>
       <c r="F9" t="n">
-        <v>3.755542849354623</v>
+        <v>2.994074530739832</v>
       </c>
       <c r="G9" t="n">
-        <v>3.429064618893106</v>
+        <v>13.05717658996582</v>
       </c>
       <c r="H9" t="n">
-        <v>3.755542849354623</v>
+        <v>7.210699558258057</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -808,12 +795,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sac_ascf_nu</t>
+          <t>NLM_sac_ascf_nu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -823,20 +810,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sac_ascf_nu.txt</t>
+          <t>NLM_sac_ascf_nu.txt</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-1.792424303806497</v>
+        <v>-0.0887406043027572</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3696222346645959</v>
+        <v>-1.792157326870182</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.792424303806497</v>
+        <v>16.58442306518555</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3696222346645959</v>
+        <v>8.958390235900879</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -848,12 +835,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sac_ascf_phi</t>
+          <t>NLM_sac_ascf_phi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -863,37 +850,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sac_ascf_phi.txt</t>
+          <t>NLM_sac_ascf_phi.txt</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-3.776542258541617</v>
+        <v>-0.7706393367729825</v>
       </c>
       <c r="F11" t="n">
-        <v>0.013445739520374</v>
+        <v>-1.676091519150569</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.776542258541617</v>
+        <v>16.15628433227539</v>
       </c>
       <c r="H11" t="n">
-        <v>0.013445739520374</v>
+        <v>9.636765480041504</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sac_ascf_rho</t>
+          <t>NLM_sac_ascf_rho</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -903,20 +890,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sac_ascf_rho.txt</t>
+          <t>NLM_sac_ascf_rho.txt</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-0.7987726375373831</v>
+        <v>0.4143123994092694</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6205621153676727</v>
+        <v>-1.876068871407113</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7987726375373831</v>
+        <v>16.89044952392578</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6205621153676727</v>
+        <v>8.641520500183105</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -928,35 +915,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sac_ascf_theta</t>
+          <t>NLM_sac_ascf_theta</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NLM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Persistent_low_frequency</t>
+          <t>Intermediate_broadband</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sac_ascf_theta.txt</t>
+          <t>NLM_sac_ascf_theta.txt</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5047073319744102</v>
+        <v>2.048870406553446</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7707937598414627</v>
+        <v>-0.4693387730294322</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5047073319744102</v>
+        <v>15.17455577850342</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7707937598414627</v>
+        <v>8.206164360046387</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -968,35 +955,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_alpha</t>
+          <t>lorenz</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>REFERENCE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Persistent_low_frequency</t>
+          <t>Lorenz_reference</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_alpha.txt</t>
+          <t>lorenz.txt</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.807026880910019</v>
+        <v>-0.2828973796601615</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.195350859570914</v>
+        <v>-4.579225264629409</v>
       </c>
       <c r="G14" t="n">
-        <v>1.807026880910019</v>
+        <v>15.8285961151123</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.195350859570914</v>
+        <v>9.394391059875488</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1008,12 +995,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_beta</t>
+          <t>sac_ascf_alpha</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1023,77 +1010,77 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_beta.txt</t>
+          <t>sac_ascf_alpha.txt</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.209621760624634</v>
+        <v>0.3539401482135198</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9287640735768554</v>
+        <v>-2.080720664980124</v>
       </c>
       <c r="G15" t="n">
-        <v>3.209621760624634</v>
+        <v>16.3662052154541</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9287640735768554</v>
+        <v>7.665895462036133</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_delta</t>
+          <t>sac_ascf_beta</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Intermediate_broadband</t>
+          <t>Persistent_low_frequency</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_delta.txt</t>
+          <t>sac_ascf_beta.txt</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.298652391128684</v>
+        <v>2.552886666351788</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.896184418203047</v>
+        <v>1.75832089689625</v>
       </c>
       <c r="G16" t="n">
-        <v>1.298652391128684</v>
+        <v>14.44797134399414</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.896184418203047</v>
+        <v>6.892201900482178</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_gamma</t>
+          <t>sac_ascf_delta</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1103,20 +1090,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_gamma.txt</t>
+          <t>sac_ascf_delta.txt</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-1.24810360734104</v>
+        <v>-0.1751784034167984</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.032546200323493</v>
+        <v>0.2773534794708468</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.24810360734104</v>
+        <v>17.39632415771484</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.032546200323493</v>
+        <v>8.526703834533691</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1128,35 +1115,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_kai</t>
+          <t>sac_ascf_gamma</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High_frequency_outlier</t>
+          <t>Intermediate_broadband</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_kai.txt</t>
+          <t>sac_ascf_gamma.txt</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-7.694321405618756</v>
+        <v>-3.984604252341704</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9978135099898858</v>
+        <v>0.8883655965513886</v>
       </c>
       <c r="G18" t="n">
-        <v>-7.694321405618756</v>
+        <v>17.58218383789062</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9978135099898858</v>
+        <v>9.600662231445312</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1168,52 +1155,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_kappa</t>
+          <t>sac_ascf_kai</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Persistent_low_frequency</t>
+          <t>High_frequency_outlier</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_kappa.txt</t>
+          <t>sac_ascf_kai.txt</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.055033125157217</v>
+        <v>-12.12540781107777</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3320232028152948</v>
+        <v>3.913115956445139</v>
       </c>
       <c r="G19" t="n">
-        <v>3.055033125157217</v>
+        <v>18.15353202819824</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3320232028152948</v>
+        <v>10.19728183746338</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_lambda</t>
+          <t>sac_ascf_kappa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1223,20 +1210,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_lambda.txt</t>
+          <t>sac_ascf_kappa.txt</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.870230583478715</v>
+        <v>2.582881340223393</v>
       </c>
       <c r="F20" t="n">
-        <v>1.216188803034467</v>
+        <v>0.9331120273645885</v>
       </c>
       <c r="G20" t="n">
-        <v>3.870230583478715</v>
+        <v>14.46398162841797</v>
       </c>
       <c r="H20" t="n">
-        <v>1.216188803034467</v>
+        <v>7.513304710388184</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1248,12 +1235,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_mu</t>
+          <t>sac_ascf_lambda</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1263,20 +1250,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_mu.txt</t>
+          <t>sac_ascf_lambda.txt</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.025983089182492</v>
+        <v>3.524993236197498</v>
       </c>
       <c r="F21" t="n">
-        <v>2.959537789780746</v>
+        <v>1.796298369228807</v>
       </c>
       <c r="G21" t="n">
-        <v>4.025983089182492</v>
+        <v>14.00830364227295</v>
       </c>
       <c r="H21" t="n">
-        <v>2.959537789780746</v>
+        <v>7.022025585174561</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1288,52 +1275,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_nu</t>
+          <t>sac_ascf_mu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Intermediate_broadband</t>
+          <t>Persistent_low_frequency</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_nu.txt</t>
+          <t>sac_ascf_mu.txt</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-0.08643230486218792</v>
+        <v>3.526523856871819</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.820566152349494</v>
+        <v>3.742552860668229</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.08643230486218792</v>
+        <v>13.32613849639893</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.820566152349494</v>
+        <v>6.716596126556396</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_phi</t>
+          <t>sac_ascf_nu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1343,20 +1330,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_phi.txt</t>
+          <t>sac_ascf_nu.txt</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-0.6783630998188103</v>
+        <v>-1.851227903444911</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.751293686587293</v>
+        <v>-0.4052315696013209</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6783630998188103</v>
+        <v>18.03271102905273</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.751293686587293</v>
+        <v>9.237345695495605</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1368,12 +1355,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_rho</t>
+          <t>sac_ascf_phi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1383,60 +1370,60 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_rho.txt</t>
+          <t>sac_ascf_phi.txt</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5930949472203999</v>
+        <v>-3.780109035021884</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.874079983579134</v>
+        <v>-0.03667454338832105</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5930949472203999</v>
+        <v>17.59712982177734</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.874079983579134</v>
+        <v>10.18813323974609</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_theta</t>
+          <t>sac_ascf_rho</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NLM_SAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Persistent_low_frequency</t>
+          <t>Intermediate_broadband</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NLM_sac_ascf_theta.txt</t>
+          <t>sac_ascf_rho.txt</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.024519492765062</v>
+        <v>-0.999451128848773</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4939980049059641</v>
+        <v>-0.6863509277711408</v>
       </c>
       <c r="G25" t="n">
-        <v>2.024519492765062</v>
+        <v>17.81390762329102</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4939980049059641</v>
+        <v>8.590236663818359</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1448,35 +1435,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lorenz</t>
+          <t>sac_ascf_theta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REFERENCE</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lorenz_reference</t>
+          <t>Intermediate_broadband</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>lorenz.txt</t>
+          <t>sac_ascf_theta.txt</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-0.4720559545492404</v>
+        <v>0.5180678938862414</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.674485592458883</v>
+        <v>0.7232221049896391</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4720559545492404</v>
+        <v>15.68406963348389</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.674485592458883</v>
+        <v>7.399672985076904</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1500,17 +1487,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>silhouette</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ARI_vs_predefined_groups</t>
         </is>
@@ -1521,10 +1508,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.43703603274515</v>
+        <v>0.4322667138882542</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1842610364683301</v>
+        <v>0.1362763915547025</v>
       </c>
     </row>
     <row r="3">
@@ -1532,7 +1519,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2898612014585119</v>
+        <v>0.2971574131211026</v>
       </c>
       <c r="C3" t="n">
         <v>0.5153249630723782</v>
@@ -1543,10 +1530,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2883496714479309</v>
+        <v>0.2875894840457734</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3195492312100086</v>
+        <v>0.4914525833253748</v>
       </c>
     </row>
     <row r="5">
@@ -1554,7 +1541,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3167320802963437</v>
+        <v>0.3196538123978483</v>
       </c>
       <c r="C5" t="n">
         <v>0.5132301547678483</v>
@@ -1565,10 +1552,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2886105888419844</v>
+        <v>0.3195460214205244</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4696339434276207</v>
+        <v>0.5733441690369768</v>
       </c>
     </row>
   </sheetData>
@@ -1582,65 +1569,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>cluster</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>size</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dominant_predefined_group</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>members</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PC1_loading</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>PC2_loading</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Persistent_low_frequency</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sac_ascf_alpha, sac_ascf_beta, sac_ascf_delta, sac_ascf_kappa, sac_ascf_lambda, sac_ascf_mu, sac_ascf_nu, sac_ascf_rho, sac_ascf_theta, NLM_sac_ascf_alpha, NLM_sac_ascf_beta, NLM_sac_ascf_delta, NLM_sac_ascf_gamma, NLM_sac_ascf_kappa, NLM_sac_ascf_lambda, NLM_sac_ascf_mu, NLM_sac_ascf_nu, NLM_sac_ascf_phi, NLM_sac_ascf_rho, NLM_sac_ascf_theta, lorenz</t>
-        </is>
+        <v>0.09547800794914577</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3617513637632316</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Intermediate_broadband</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>sac_ascf_gamma, sac_ascf_kai, sac_ascf_phi, NLM_sac_ascf_kai</t>
-        </is>
+        <v>0.195536710894871</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3060121805368109</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.08645316860384311</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3585818139150784</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>iqr</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1869284402253952</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3147724442983894</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>skewness</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.01346808753825927</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2745359210940197</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>excess_kurtosis</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.009405012998762221</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.2677214843982836</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>diff_std</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.08893530662793879</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2745058524529024</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.2488170272502953</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1430296935172086</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>autocorr_lag1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2241631029163122</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.1911239787027156</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>autocorr_lag5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2555486267860718</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.09200737446100959</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>autocorr_lag10</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2598049845987032</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.06905447578281459</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>autocorr_lag20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.258042114879498</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.02278791935103376</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>autocorr_lag50</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2348842554938871</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.1157753348971097</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>autocorr_lag100</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.2068972368446659</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1659006872624098</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>spectral_entropy</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.2534124026352432</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.03534402525898175</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dominant_frequency</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.1805341775128191</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.2029222426537914</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>spectral_energy_0.00_0.01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.2612333224917465</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.03945001880419254</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>spectral_energy_0.01_0.05</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.168363309263523</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.1738686443716012</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>spectral_energy_0.05_0.20</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.2400872783718668</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.04053690613354061</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>spectral_energy_0.20_0.50</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.2176264635051152</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.1970180458029842</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>zero_crossing_rate</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.2485917547206276</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1454709064934466</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>permutation_entropy_m5</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.04477966566189027</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2620333180194735</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dfa_exponent</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.2605479054633112</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.05749507509854913</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>nonlinear_prediction_error</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.2498741882564507</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.07722779387752757</v>
       </c>
     </row>
   </sheetData>
@@ -1654,83 +1907,288 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>cluster</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>size</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dominant_predefined_group</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>members</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>explained_variance_ratio</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cumulative_variance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Intermediate_broadband</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sac_ascf_gamma, sac_ascf_kai, sac_ascf_phi, NLM_sac_ascf_kai</t>
-        </is>
+        <v>0.5717612957500511</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5717612957500511</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Intermediate_broadband</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>sac_ascf_alpha, sac_ascf_delta, sac_ascf_nu, sac_ascf_rho, sac_ascf_theta, NLM_sac_ascf_alpha, NLM_sac_ascf_delta, NLM_sac_ascf_gamma, NLM_sac_ascf_nu, NLM_sac_ascf_phi, NLM_sac_ascf_rho, NLM_sac_ascf_theta, lorenz</t>
-        </is>
+        <v>0.1634141764794848</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7351754722295358</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
+        <v>0.1076722180595257</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8428476902890615</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.06491215177481985</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9077598420638813</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.03017863484388389</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9379384769077652</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.02733713066763881</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.965275607575404</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.01387645623166241</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9791520638070664</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Persistent_low_frequency</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>sac_ascf_beta, sac_ascf_kappa, sac_ascf_lambda, sac_ascf_mu, NLM_sac_ascf_beta, NLM_sac_ascf_kappa, NLM_sac_ascf_lambda, NLM_sac_ascf_mu</t>
-        </is>
+      <c r="B9" t="n">
+        <v>0.008125671539985174</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9872777353470517</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.004491982369655196</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9917697177167069</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.003589151535335438</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9953588692520423</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.001690146719557663</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9970490159716</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.001500648573070093</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9985496645446701</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0006199558043338715</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9991696203490039</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0003757409532158437</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9995453613022197</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.0002557523511036543</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9998011136533234</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0001106046582298722</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9999117183115532</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5.732544158393826e-05</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9999690437531372</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.885073974379073e-05</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9999878944928811</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7.821431748564411e-06</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9999957159246297</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4.222860193234011e-06</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9999999387848229</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5.766832009521159e-08</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.999999996453143</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.09061656579876e-09</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9999999995437595</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4.562371140743255e-10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9999999999999967</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.33368924697122e-15</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1744,780 +2202,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>PC1_loading</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>PC2_loading</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>abs_PC1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>abs_PC2</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>spectral_energy_0_0.01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.2627231376638968</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.03541677777459968</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.2627231376638968</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.03541677777459968</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UMAP_status</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UMAP</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>autocorr_lag10</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UMAP_n_neighbors</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2610170044004568</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.06582806478830876</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.2610170044004568</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.06582806478830876</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>autocorr_lag20</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UMAP_min_dist</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2593457223837978</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.02725637795612896</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2593457223837978</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.02725637795612896</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>autocorr_lag5</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UMAP_random_state</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2567907648909079</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.08941843993936816</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2567907648909079</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.08941843993936816</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>dfa_exponent</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KMeans_best_k</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2547478241651535</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.08169065544742894</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.2547478241651535</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.08169065544742894</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>spectral_entropy</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-0.2531244488940801</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.03857975750667494</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2531244488940801</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.03857975750667494</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-0.249787849496686</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.1440400578202121</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.249787849496686</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.1440400578202121</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zero_crossing_rate</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.2492997072548369</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.146186348742192</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.2492997072548369</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.146186348742192</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>nonlinear_prediction_error</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-0.2466456110658871</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1170162440373229</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2466456110658871</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.1170162440373229</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>spectral_energy_0.05_0.20</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-0.2409750136687374</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.03800733886925267</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.2409750136687374</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.03800733886925267</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>autocorr_lag50</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.2356248854184475</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1203054710337876</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2356248854184475</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1203054710337876</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>autocorr_lag1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.2255820133804819</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.1907497766524679</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.2255820133804819</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1907497766524679</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>spectral_energy_0.20_0.50</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.2190496990377818</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.1968003747630946</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.2190496990377818</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.1968003747630946</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>autocorr_lag100</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.2051490951451725</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1681710406812197</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.2051490951451725</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1681710406812197</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>std</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.1953927902113917</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.3054059709032061</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.1953927902113917</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.3054059709032061</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>iqr</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.1858062973287552</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.3134023376791953</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1858062973287552</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.3134023376791953</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>dominant_frequency</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-0.1816906834200765</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.2020078873843498</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1816906834200765</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.2020078873843498</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>spectral_energy_0.01_0.05</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-0.1694916323988187</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.1811598911852079</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1694916323988187</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.1811598911852079</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.09559850970768628</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.356111884474477</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.09559850970768628</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.356111884474477</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>diff_std</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>-0.08782698545709296</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.2798885569814923</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.08782698545709296</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2798885569814923</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.08617498481418925</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.3525261185674394</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.08617498481418925</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.3525261185674394</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>permutation_entropy_m5</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-0.04277893444640838</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.2679113118663537</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.04277893444640838</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.2679113118663537</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>skewness</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>-0.01095919011037489</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.2640446911352051</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.01095919011037489</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.2640446911352051</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>excess_kurtosis</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-0.009153655161992114</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.2575692826619445</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.009153655161992114</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.2575692826619445</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>explained_variance_ratio</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>cumulative_variance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.5689170343424692</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.5689170343424692</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
         <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.1651668479196451</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.7340838822621143</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.1080403243248489</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.8421242065869632</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.06362589844875469</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9057501050357178</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.03076538262222568</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9365154876579436</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.02787169246531692</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9643871801232605</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.01485971146310013</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.9792468915863607</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.007491482408101094</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9867383739944617</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.004526758371890627</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.9912651323663524</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.004274584935869904</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.9955397173022222</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.001585274202564142</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.9971249915047864</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.001527670931752942</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.9986526624365394</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.0006188931674426658</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.9992715556039821</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.0004095758678204159</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.9996811314718025</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.0001857795204808578</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.9998669109922833</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>6.490485859175268e-05</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.9999318158508751</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3.468147141641037e-05</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.9999664973222915</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2.054059787234319e-05</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.9999870379201639</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>7.489131621372429e-06</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.9999945270517853</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>5.366017807967362e-06</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.9999998930695932</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="n">
-        <v>9.326209781260157e-08</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.9999999863316911</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
-        <v>1.344634044101782e-08</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.9999999997780316</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="n">
-        <v>2.219637271545657e-10</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.9999999999999953</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="n">
-        <v>5.048413247230403e-15</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
